--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566254</v>
+        <v>122565857</v>
       </c>
       <c r="B2" t="n">
-        <v>91110</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577926</v>
+        <v>577965</v>
       </c>
       <c r="R2" t="n">
-        <v>7047589</v>
+        <v>7047592</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122565767</v>
+        <v>122566312</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577991</v>
+        <v>577901</v>
       </c>
       <c r="R3" t="n">
-        <v>7047591</v>
+        <v>7047598</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566312</v>
+        <v>122566254</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>91123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>577926</v>
       </c>
       <c r="R4" t="n">
-        <v>7047598</v>
+        <v>7047589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565857</v>
+        <v>122565767</v>
       </c>
       <c r="B5" t="n">
-        <v>90844</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577965</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>7047592</v>
+        <v>7047591</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122565857</v>
+        <v>122566312</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>56593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577965</v>
+        <v>577901</v>
       </c>
       <c r="R2" t="n">
-        <v>7047592</v>
+        <v>7047598</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566312</v>
+        <v>122566254</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>91123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577901</v>
+        <v>577926</v>
       </c>
       <c r="R3" t="n">
-        <v>7047598</v>
+        <v>7047589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566254</v>
+        <v>122565767</v>
       </c>
       <c r="B4" t="n">
-        <v>91123</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577926</v>
+        <v>577991</v>
       </c>
       <c r="R4" t="n">
-        <v>7047589</v>
+        <v>7047591</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565767</v>
+        <v>122565857</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577965</v>
       </c>
       <c r="R5" t="n">
-        <v>7047591</v>
+        <v>7047592</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566254</v>
+        <v>122565857</v>
       </c>
       <c r="B3" t="n">
-        <v>91123</v>
+        <v>90851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577926</v>
+        <v>577965</v>
       </c>
       <c r="R3" t="n">
-        <v>7047589</v>
+        <v>7047592</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122565767</v>
+        <v>122566254</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>91124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577991</v>
+        <v>577926</v>
       </c>
       <c r="R4" t="n">
-        <v>7047591</v>
+        <v>7047589</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565857</v>
+        <v>122565767</v>
       </c>
       <c r="B5" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577965</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>7047592</v>
+        <v>7047591</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122565857</v>
+        <v>122565767</v>
       </c>
       <c r="B3" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577965</v>
+        <v>577991</v>
       </c>
       <c r="R3" t="n">
-        <v>7047592</v>
+        <v>7047591</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566254</v>
+        <v>122565857</v>
       </c>
       <c r="B4" t="n">
-        <v>91124</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577926</v>
+        <v>577965</v>
       </c>
       <c r="R4" t="n">
-        <v>7047589</v>
+        <v>7047592</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565767</v>
+        <v>122566254</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>91124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577926</v>
       </c>
       <c r="R5" t="n">
-        <v>7047591</v>
+        <v>7047589</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122566312</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122565767</v>
+        <v>122566254</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>91125</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577991</v>
+        <v>577926</v>
       </c>
       <c r="R3" t="n">
-        <v>7047591</v>
+        <v>7047589</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
         <v>122565857</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566254</v>
+        <v>122565767</v>
       </c>
       <c r="B5" t="n">
-        <v>91124</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577926</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>7047589</v>
+        <v>7047591</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566312</v>
+        <v>122565767</v>
       </c>
       <c r="B2" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577901</v>
+        <v>577991</v>
       </c>
       <c r="R2" t="n">
-        <v>7047598</v>
+        <v>7047591</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566254</v>
+        <v>122566312</v>
       </c>
       <c r="B3" t="n">
-        <v>91125</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577926</v>
+        <v>577901</v>
       </c>
       <c r="R3" t="n">
-        <v>7047589</v>
+        <v>7047598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122565857</v>
+        <v>122566254</v>
       </c>
       <c r="B4" t="n">
-        <v>90852</v>
+        <v>91128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577965</v>
+        <v>577926</v>
       </c>
       <c r="R4" t="n">
-        <v>7047592</v>
+        <v>7047589</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565767</v>
+        <v>122565857</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577965</v>
       </c>
       <c r="R5" t="n">
-        <v>7047591</v>
+        <v>7047592</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122565767</v>
+        <v>122566254</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>91128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577991</v>
+        <v>577926</v>
       </c>
       <c r="R2" t="n">
-        <v>7047591</v>
+        <v>7047589</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566254</v>
+        <v>122565767</v>
       </c>
       <c r="B4" t="n">
-        <v>91128</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577926</v>
+        <v>577991</v>
       </c>
       <c r="R4" t="n">
-        <v>7047589</v>
+        <v>7047591</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566312</v>
+        <v>122565857</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577901</v>
+        <v>577965</v>
       </c>
       <c r="R2" t="n">
-        <v>7047598</v>
+        <v>7047592</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +790,7 @@
         <v>122566254</v>
       </c>
       <c r="B3" t="n">
-        <v>91231</v>
+        <v>91235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122565767</v>
+        <v>122566312</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +911,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577991</v>
+        <v>577901</v>
       </c>
       <c r="R4" t="n">
-        <v>7047591</v>
+        <v>7047598</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565857</v>
+        <v>122565767</v>
       </c>
       <c r="B5" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577965</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>7047592</v>
+        <v>7047591</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122565857</v>
+        <v>122566312</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577965</v>
+        <v>577901</v>
       </c>
       <c r="R2" t="n">
-        <v>7047592</v>
+        <v>7047598</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566312</v>
+        <v>122565767</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,46 +916,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>577991</v>
       </c>
       <c r="R4" t="n">
-        <v>7047598</v>
+        <v>7047591</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565767</v>
+        <v>122565857</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577965</v>
       </c>
       <c r="R5" t="n">
-        <v>7047591</v>
+        <v>7047592</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122566312</v>
+        <v>122565857</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577901</v>
+        <v>577965</v>
       </c>
       <c r="R2" t="n">
-        <v>7047598</v>
+        <v>7047592</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565857</v>
+        <v>122566312</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1023,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577965</v>
+        <v>577901</v>
       </c>
       <c r="R5" t="n">
-        <v>7047592</v>
+        <v>7047598</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122566254</v>
+        <v>122565767</v>
       </c>
       <c r="B3" t="n">
-        <v>91235</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577926</v>
+        <v>577991</v>
       </c>
       <c r="R3" t="n">
-        <v>7047589</v>
+        <v>7047591</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122565767</v>
+        <v>122566254</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>91235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577991</v>
+        <v>577926</v>
       </c>
       <c r="R4" t="n">
-        <v>7047591</v>
+        <v>7047589</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122565857</v>
+        <v>122566254</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577965</v>
+        <v>577926</v>
       </c>
       <c r="R2" t="n">
-        <v>7047592</v>
+        <v>7047589</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +785,11 @@
         <v>122565767</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122566254</v>
+        <v>122566495</v>
       </c>
       <c r="B4" t="n">
-        <v>91235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallrå, Kallrå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577926</v>
+        <v>577898</v>
       </c>
       <c r="R4" t="n">
-        <v>7047589</v>
+        <v>7047638</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,43 +1006,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122566312</v>
+        <v>122568941</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577901</v>
+        <v>577874</v>
       </c>
       <c r="R5" t="n">
-        <v>7047598</v>
+        <v>7047636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,15 +1111,127 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122566312</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kallrå, Kallrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577901</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7047598</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5018-2025 artfynd.xlsx
+++ b/artfynd/A 5018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566254</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122565767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566495</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122568941</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,8 +1257,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122566312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>